--- a/packages/calculators/src/modules/test/3.3-dairy-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.3-dairy-enteric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{AD72D771-8AA8-E443-9012-A1BBD890DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E4A630E3-CC00-1248-BDAE-262A25DF97E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="13560" windowWidth="28800" windowHeight="22980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
